--- a/212-corriger-interopsanteorg/ig/ValueSet-VS-TRE-R301-SourceInformationInstallation.xlsx
+++ b/212-corriger-interopsanteorg/ig/ValueSet-VS-TRE-R301-SourceInformationInstallation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:13:56+00:00</t>
+    <t>2024-07-01T16:18:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
